--- a/LubanConfig/Moba/Production/Datas/J-召唤物表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/J-召唤物表.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -812,6 +812,58 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n">
+        <v>1008</v>
+      </c>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n">
+        <v>1008</v>
+      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>1008</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号-空中支援飞艇</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>10080401</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2" t="n"/>
+      <c r="P5" s="2" t="n">
+        <v>1008</v>
+      </c>
+      <c r="Q5" s="2" t="n"/>
+      <c r="R5" s="2" t="n"/>
+      <c r="S5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -934,7 +986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA4"/>
+  <dimension ref="A1:AA5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1456,6 +1508,85 @@
       <c r="Z4" s="2" t="n"/>
       <c r="AA4" s="2" t="n"/>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n">
+        <v>1008</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>鲁班七号-空中支援召唤动作</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="2" t="n">
+        <v>1008</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="2" t="n"/>
+      <c r="AA5" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/LubanConfig/Moba/Production/Datas/J-召唤物表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/J-召唤物表.xlsx
@@ -826,13 +826,13 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>6000</v>
+        <v>14000</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1008</v>
+        <v>100801</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
